--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -33471,7 +33471,7 @@
       </c>
       <c r="G691" s="3" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="H691" s="5" t="n">

--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,36 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -171,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11395,7 +11261,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -31251,7 +31117,7 @@
       </c>
       <c r="G643" s="3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H643" s="5" t="n">
@@ -32263,7 +32129,7 @@
       </c>
       <c r="G665" s="3" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="H665" s="5" t="n">
@@ -33889,7 +33755,7 @@
       </c>
       <c r="G700" s="3" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H700" s="5" t="n">
@@ -36331,6732 +36197,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:P30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>柏蔚森 II - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>375 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>51 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>211 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>106 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L6" s="16" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M6" s="16" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N6" s="16" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O6" s="16" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P6" s="16" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K7" s="16" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L7" s="16" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M7" s="16" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N7" s="16" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O7" s="16" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P7" s="16" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L8" s="16" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M8" s="16" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N8" s="16" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O8" s="16" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P8" s="16" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M9" s="16" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N9" s="16" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O9" s="16" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P9" s="16" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L10" s="16" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M10" s="16" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N10" s="16" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O10" s="16" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P10" s="16" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M11" s="16" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N11" s="16" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O11" s="16" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P11" s="17" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M12" s="16" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N12" s="16" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O12" s="16" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P12" s="17" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$921万
-$24,050/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-暂无价格
-暂无呎价
-(在售)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L13" s="16" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M13" s="16" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N13" s="16" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O13" s="16" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P13" s="17" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$1,184万
-$26,417/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$896万
-$23,394/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$899万
-$23,462/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$618万
-$23,595/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$924万
-$23,579/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I14" s="19" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$1,084万
-$28,153/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$842万
-$29,334/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K14" s="17" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M14" s="19" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-$1,090万
-$27,605/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="N14" s="19" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-$1,151万
-$28,561/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="O14" s="17" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P14" s="18" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$1,019万
-$23,327/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-$898万
-$22,722/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$874万
-$22,825/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$877万
-$22,890/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$570万
-$21,744/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I15" s="19" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$1,052万
-$27,332/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J15" s="17" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$826万
-$28,777/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M15" s="19" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-$1,059万
-$26,803/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="N15" s="19" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-$1,118万
-$27,730/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="O15" s="17" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P15" s="18" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$1,047万
-$23,968/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-$870万
-$22,355/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-$876万
-$22,167/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$853万
-$22,266/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$808万
-$21,097/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$556万
-$21,218/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$889万
-$22,668/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$818万
-$28,505/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M16" s="17" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="N16" s="17" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O16" s="18" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-$952万
-$23,867/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="P16" s="18" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$1,027万
-$23,503/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-$820万
-$21,080/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-$858万
-$21,734/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$790万
-$20,616/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$792万
-$20,681/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$545万
-$20,802/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$862万
-$22,003/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="J17" s="18" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$658万
-$22,927/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K17" s="18" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-$864万
-$22,370/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L17" s="18" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-$852万
-$22,370/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M17" s="17" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="N17" s="17" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O17" s="18" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-$915万
-$22,942/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="P17" s="18" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$997万
-$22,819/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$949万
-$21,192/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-$804万
-$20,668/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-$748万
-$18,927/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$746万
-$19,480/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$792万
-$20,668/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$522万
-$19,908/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$799万
-$20,372/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="J18" s="18" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$645万
-$22,488/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K18" s="18" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-$847万
-$21,933/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L18" s="18" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-$836万
-$21,932/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="M18" s="17" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="N18" s="18" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-$896万
-$22,241/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O18" s="18" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-$840万
-$21,048/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="P18" s="18" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$906万
-$20,728/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$870万
-$19,426/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-$736万
-$18,910/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-$733万
-$18,549/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$731万
-$19,094/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$719万
-$18,773/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$512万
-$19,523/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$783万
-$19,977/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="J19" s="18" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$633万
-$22,059/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K19" s="18" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-$822万
-$21,288/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L19" s="18" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-$811万
-$21,289/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="M19" s="18" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-$850万
-$21,514/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N19" s="18" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-$870万
-$21,593/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O19" s="18" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-$815万
-$20,436/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="P19" s="18" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$879万
-$20,124/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$878万
-$19,607/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-$721万
-$18,530/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-$718万
-$18,180/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$717万
-$18,713/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$705万
-$18,405/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$513万
-$19,595/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$768万
-$19,582/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$819万
-$21,275/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="J20" s="18" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$611万
-$21,286/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="K20" s="18" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-$761万
-$19,710/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="L20" s="18" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-$751万
-$19,711/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="M20" s="18" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-$801万
-$20,286/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="N20" s="18" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-$790万
-$19,613/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="O20" s="18" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-$792万
-$19,840/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="P20" s="18" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$854万
-$19,535/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$836万
-$18,672/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-$698万
-$17,931/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-$695万
-$17,590/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$685万
-$17,890/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$691万
-$18,044/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$500万
-$19,095/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$743万
-$18,957/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$755万
-$19,610/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J21" s="18" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$606万
-$21,105/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="K21" s="18" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-$739万
-$19,137/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="L21" s="18" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-$729万
-$19,136/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="M21" s="18" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-$756万
-$19,137/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="N21" s="18" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-$775万
-$19,228/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="O21" s="18" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-$776万
-$19,449/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="P21" s="18" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$837万
-$19,153/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$832万
-$18,580/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-$684万
-$17,571/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-$683万
-$17,281/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$673万
-$17,577/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$661万
-$17,269/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$470万
-$17,958/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$730万
-$18,630/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$737万
-$19,132/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="J22" s="18" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$560万
-$19,498/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="K22" s="18" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-$717万
-$18,580/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="L22" s="18" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-$708万
-$18,580/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="M22" s="18" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-$734万
-$18,580/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="N22" s="18" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-$760万
-$18,851/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="O22" s="18" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-$761万
-$19,068/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="P22" s="18" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$821万
-$18,778/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$808万
-$18,038/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-$663万
-$17,049/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-$671万
-$16,980/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$662万
-$17,274/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$642万
-$16,765/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$476万
-$18,179/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$718万
-$18,309/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$718万
-$18,662/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J23" s="18" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$555万
-$19,341/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="K23" s="18" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-$696万
-$18,039/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="L23" s="18" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-$687万
-$18,037/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M23" s="18" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-$712万
-$18,038/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="N23" s="18" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-$745万
-$18,481/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="O23" s="18" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-$746万
-$18,694/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="P23" s="18" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$804万
-$18,410/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$896万
-$20,000/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-$657万
-$16,879/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-$659万
-$16,681/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$650万
-$16,971/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$639万
-$16,681/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$454万
-$17,347/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$705万
-$17,992/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I24" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$700万
-$18,182/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="J24" s="18" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$539万
-$18,777/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="K24" s="18" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-$712万
-$18,451/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="L24" s="18" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-$762万
-$20,000/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="M24" s="18" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-$729万
-$18,451/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="N24" s="18" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-$716万
-$17,772/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="O24" s="18" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-$738万
-$18,509/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="P24" s="18" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$796万
-$18,217/呎
-(25年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$905万
-$20,201/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-$654万
-$16,820/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-$652万
-$16,501/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$674万
-$17,595/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$636万
-$16,601/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$452万
-$17,263/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$686万
-$17,513/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$693万
-$17,997/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="J25" s="18" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$534万
-$18,596/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="K25" s="18" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-$772万
-$20,000/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L25" s="18" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-$703万
-$18,451/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="M25" s="18" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-$798万
-$20,203/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N25" s="18" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-$709万
-$17,596/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="O25" s="18" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-$718万
-$18,003/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="P25" s="18" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$788万
-$18,034/呎
-(25年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$784万
-$17,509/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-$648万
-$16,656/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-$648万
-$16,418/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$670万
-$17,507/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$656万
-$17,120/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$450万
-$17,172/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$683万
-$17,426/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I26" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$686万
-$17,816/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="J26" s="18" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$528万
-$18,404/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="K26" s="18" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-$772万
-$20,000/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L26" s="18" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-$762万
-$20,000/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="M26" s="18" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-$798万
-$20,203/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N26" s="18" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-$706万
-$17,506/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="O26" s="18" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-$715万
-$17,912/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="P26" s="18" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$769万
-$17,593/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$780万
-$17,420/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-$645万
-$16,571/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-$645万
-$16,337/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$667万
-$17,420/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$652万
-$17,034/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$464万
-$17,714/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$680万
-$17,339/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I27" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$682万
-$17,727/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="J27" s="18" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$523万
-$18,223/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="K27" s="18" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-$733万
-$19,000/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="L27" s="18" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-$686万
-$18,000/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="M27" s="17" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="N27" s="18" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-$725万
-$18,000/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="O27" s="18" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-$698万
-$17,504/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="P27" s="18" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$765万
-$17,503/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$777万
-$17,335/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-$641万
-$16,488/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-$642万
-$16,253/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$664万
-$17,334/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$636万
-$16,619/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$446万
-$17,004/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$676万
-$17,253/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I28" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$770万
-$20,000/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="J28" s="18" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$533万
-$18,568/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="K28" s="18" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-$772万
-$20,000/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L28" s="18" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-$724万
-$19,000/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="M28" s="17" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="N28" s="18" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-$725万
-$18,000/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="O28" s="18" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-$695万
-$17,416/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="P28" s="18" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$761万
-$17,416/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>A | 447呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$675万
-$17,297/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-$674万
-$17,053/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$663万
-$17,300/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 384呎 (2房)
-$650万
-$16,917/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$438万
-$16,721/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H29" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$706万
-$18,000/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="J29" s="18" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$530万
-$18,474/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="K29" s="18" t="inlineStr">
-        <is>
-          <t>K | 387呎 (2房)
-$716万
-$18,501/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="L29" s="18" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-$705万
-$18,501/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="M29" s="17" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="N29" s="17" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O29" s="18" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-$738万
-$18,501/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="P29" s="18" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$757万
-$17,330/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>A | 447呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$659万
-$16,903/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-$668万
-$16,904/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$647万
-$16,903/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>E | 384呎 (2房)
-$636万
-$16,565/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G30" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$454万
-$17,321/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H30" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$706万
-$18,000/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="J30" s="18" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$543万
-$18,923/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="K30" s="17" t="inlineStr">
-        <is>
-          <t>K | 387呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="L30" s="18" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-$770万
-$20,202/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="M30" s="17" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="N30" s="17" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O30" s="18" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-$806万
-$20,201/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="P30" s="18" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$883万
-$20,201/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:P30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>柏蔚森 II - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>375 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>48 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>234 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>88 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L6" s="16" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M6" s="16" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N6" s="16" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O6" s="16" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P6" s="16" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K7" s="16" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L7" s="16" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M7" s="16" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N7" s="16" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O7" s="16" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P7" s="16" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L8" s="16" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M8" s="16" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N8" s="16" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O8" s="16" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P8" s="16" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M9" s="16" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N9" s="16" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O9" s="16" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P9" s="16" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L10" s="16" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M10" s="16" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O10" s="17" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P10" s="16" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-$1,136万
-$25,177/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$820万
-$31,290/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M11" s="16" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N11" s="17" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O11" s="17" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P11" s="16" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-$1,108万
-$24,561/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$954万
-$24,903/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$800万
-$30,527/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K12" s="17" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M12" s="17" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="N12" s="18" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-$866万
-$22,608/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O12" s="18" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-$882万
-$23,037/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="P12" s="17" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-$1,081万
-$23,962/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$930万
-$24,295/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-$899万
-$22,931/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$927万
-$24,211/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$640万
-$24,420/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$888万
-$22,663/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K13" s="17" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="L13" s="16" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M13" s="17" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="N13" s="18" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-$849万
-$22,167/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O13" s="18" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-$865万
-$22,587/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="P13" s="17" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$1,027万
-$26,815/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$1,013万
-$26,452/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$761万
-$29,057/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L14" s="16" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M14" s="16" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N14" s="16" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O14" s="16" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P14" s="16" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-$972万
-$21,545/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$822万
-$21,449/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-$830万
-$21,186/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-$880万
-$22,220/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$826万
-$21,569/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$572万
-$21,813/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$837万
-$21,362/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$830万
-$21,564/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="J15" s="18" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-$655万
-$23,145/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K15" s="18" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-$880万
-$22,384/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M15" s="17" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="N15" s="18" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-$771万
-$20,125/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="O15" s="18" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-$785万
-$20,504/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="P15" s="18" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-$962万
-$21,725/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-$948万
-$21,022/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$817万
-$21,334/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-$806万
-$20,569/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-$858万
-$21,679/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$806万
-$21,044/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$561万
-$21,420/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$817万
-$20,842/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$871万
-$22,613/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J16" s="18" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-$649万
-$22,933/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K16" s="18" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-$814万
-$20,725/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M16" s="18" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-$783万
-$19,718/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="N16" s="18" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-$707万
-$18,460/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="O16" s="18" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-$720万
-$18,809/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="P16" s="18" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-$944万
-$21,298/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-$909万
-$20,162/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$793万
-$20,713/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-$764万
-$19,485/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-$787万
-$19,864/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$806万
-$21,034/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$559万
-$21,344/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$744万
-$18,972/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$849万
-$22,062/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J17" s="18" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-$626万
-$22,134/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="K17" s="18" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-$799万
-$20,321/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L17" s="18" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-$823万
-$20,125/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M17" s="18" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-$817万
-$20,574/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="N17" s="18" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-$693万
-$18,099/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="O17" s="18" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-$719万
-$18,781/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="P17" s="18" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-$874万
-$19,720/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-$904万
-$20,055/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$770万
-$20,107/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-$755万
-$19,270/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-$783万
-$19,763/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$792万
-$20,668/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$497万
-$18,958/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$731万
-$18,645/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I18" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$797万
-$20,706/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="J18" s="18" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-$614万
-$21,710/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="K18" s="18" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-$783万
-$19,921/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="L18" s="17" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M18" s="18" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-$760万
-$19,136/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="N18" s="18" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-$688万
-$17,961/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="O18" s="18" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-$705万
-$18,410/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="P18" s="18" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-$856万
-$19,334/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-$895万
-$19,854/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$787万
-$20,538/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-$751万
-$19,153/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-$773万
-$19,525/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$699万
-$18,253/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$487万
-$18,584/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$729万
-$18,589/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$778万
-$20,197/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="J19" s="18" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-$573万
-$20,233/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="K19" s="18" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-$768万
-$19,532/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="L19" s="17" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M19" s="18" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-$748万
-$18,854/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="N19" s="18" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-$700万
-$18,279/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="O19" s="18" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-$679万
-$17,726/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="P19" s="18" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-$840万
-$18,953/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-$892万
-$19,772/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$723万
-$18,867/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-$736万
-$18,768/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-$769万
-$19,417/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$685万
-$17,893/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$477万
-$18,214/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$714万
-$18,227/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$726万
-$18,852/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="J20" s="18" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-$542万
-$19,152/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="K20" s="18" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-$752万
-$19,148/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L20" s="18" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-$821万
-$20,081/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="M20" s="18" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-$738万
-$18,577/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="N20" s="18" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-$664万
-$17,342/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="O20" s="18" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-$688万
-$17,977/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="P20" s="18" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-$779万
-$17,580/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-$927万
-$20,554/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$708万
-$18,499/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-$721万
-$18,393/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-$766万
-$19,333/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$672万
-$17,540/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$468万
-$17,859/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$700万
-$17,870/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$720万
-$18,709/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J21" s="18" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-$531万
-$18,777/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="K21" s="18" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-$738万
-$18,771/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L21" s="18" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-$760万
-$18,592/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M21" s="18" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-$727万
-$18,302/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="N21" s="18" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-$654万
-$17,086/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="O21" s="18" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-$666万
-$17,376/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="P21" s="18" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-$771万
-$17,406/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-$853万
-$18,914/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$692万
-$18,063/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-$707万
-$18,028/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-$722万
-$18,242/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$659万
-$17,196/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$459万
-$17,504/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$715万
-$18,247/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$715万
-$18,564/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J22" s="18" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-$527万
-$18,629/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="K22" s="18" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-$723万
-$18,405/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="L22" s="18" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-$746万
-$18,227/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M22" s="18" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-$716万
-$18,030/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="N22" s="18" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-$648万
-$16,916/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="O22" s="18" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-$659万
-$17,201/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="P22" s="20" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-$930万
-$20,982/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-$835万
-$18,508/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$668万
-$17,436/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-$692万
-$17,666/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-$701万
-$17,707/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$667万
-$17,407/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$445万
-$16,989/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$673万
-$17,173/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$710万
-$18,444/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="J23" s="18" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-$524万
-$18,523/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="K23" s="18" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-$709万
-$18,043/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="L23" s="17" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M23" s="18" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-$705万
-$17,763/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="N23" s="18" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-$641万
-$16,747/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="O23" s="18" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-$652万
-$17,031/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="P23" s="18" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-$741万
-$16,722/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-$802万
-$17,776/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$664万
-$17,350/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-$656万
-$16,724/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-$693万
-$17,497/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$636万
-$16,608/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$443万
-$16,905/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$670万
-$17,089/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="I24" s="20" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$807万
-$20,958/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="J24" s="18" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-$486万
-$17,166/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="K24" s="18" t="inlineStr">
-        <is>
-          <t>K | 393呎 (2房)
-$688万
-$17,517/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="L24" s="18" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-$710万
-$17,350/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="M24" s="18" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-$685万
-$17,247/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="N24" s="18" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-$635万
-$16,582/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="O24" s="18" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-$643万
-$16,789/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="P24" s="18" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-$734万
-$16,558/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-$784万
-$17,379/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$685万
-$17,896/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-$665万
-$16,969/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-$673万
-$17,005/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$633万
-$16,527/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$441万
-$16,821/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$667万
-$17,005/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$639万
-$16,608/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="J25" s="18" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-$472万
-$16,664/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="K25" s="18" t="inlineStr">
-        <is>
-          <t>K | 394呎 (2房)
-$687万
-$17,429/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="L25" s="17" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M25" s="18" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-$683万
-$17,194/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="N25" s="18" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-$648万
-$16,906/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="O25" s="18" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-$646万
-$16,864/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="P25" s="18" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-$732万
-$16,533/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-$761万
-$16,882/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$669万
-$17,473/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-$649万
-$16,559/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-$657万
-$16,598/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$630万
-$16,444/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$441万
-$16,844/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$650万
-$16,594/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I26" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$636万
-$16,527/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="J26" s="18" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-$469万
-$16,580/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="K26" s="18" t="inlineStr">
-        <is>
-          <t>K | 394呎 (2房)
-$683万
-$17,343/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="L26" s="17" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M26" s="17" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="N26" s="18" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-$654万
-$17,089/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="O26" s="18" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-$631万
-$16,486/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="P26" s="18" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-$730万
-$16,483/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-$754万
-$16,712/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$666万
-$17,384/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-$646万
-$16,474/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-$654万
-$16,513/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$627万
-$16,360/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$436万
-$16,656/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$647万
-$16,508/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I27" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$633万
-$16,444/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="J27" s="18" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-$467万
-$16,498/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="K27" s="18" t="inlineStr">
-        <is>
-          <t>K | 394呎 (2房)
-$680万
-$17,256/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="L27" s="17" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M27" s="18" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-$715万
-$18,000/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="N27" s="18" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-$640万
-$16,700/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="O27" s="18" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-$629万
-$16,433/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="P27" s="18" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-$728万
-$16,436/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-$747万
-$16,554/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$662万
-$17,298/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-$829万
-$21,148/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-$651万
-$16,429/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$811万
-$21,164/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$434万
-$16,573/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$644万
-$16,426/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I28" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$656万
-$17,039/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="J28" s="18" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-$484万
-$17,120/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="K28" s="18" t="inlineStr">
-        <is>
-          <t>K | 394呎 (2房)
-$677万
-$17,173/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="L28" s="17" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M28" s="17" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="N28" s="18" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-$638万
-$16,650/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="O28" s="18" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-$615万
-$16,050/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="P28" s="18" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-$726万
-$16,386/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 450呎 (2房)
-$744万
-$16,538/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$648万
-$16,924/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-$639万
-$16,309/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-$649万
-$16,394/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$622万
-$16,245/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$425万
-$16,210/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H29" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$642万
-$16,390/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="I29" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$640万
-$16,618/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="J29" s="18" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-$482万
-$17,032/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="K29" s="18" t="inlineStr">
-        <is>
-          <t>K | 394呎 (2房)
-$709万
-$18,000/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="L29" s="17" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M29" s="17" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="N29" s="18" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-$636万
-$16,601/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="O29" s="18" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-$636万
-$16,601/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="P29" s="18" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-$724万
-$16,336/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>A | 450呎 (2房)
-$741万
-$16,467/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>B | 383呎 (2房)
-$627万
-$16,371/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 392呎 (2房)
-$634万
-$16,176/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 396呎 (2房)
-$661万
-$16,702/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$624万
-$16,303/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G30" s="18" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$424万
-$16,202/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H30" s="18" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$642万
-$16,375/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="I30" s="18" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$712万
-$18,501/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="J30" s="18" t="inlineStr">
-        <is>
-          <t>J | 283呎 (1房)
-$478万
-$16,898/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="K30" s="17" t="inlineStr">
-        <is>
-          <t>K | 394呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="L30" s="17" t="inlineStr">
-        <is>
-          <t>L | 409呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="M30" s="17" t="inlineStr">
-        <is>
-          <t>M | 397呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="N30" s="18" t="inlineStr">
-        <is>
-          <t>N | 383呎 (2房)
-$634万
-$16,564/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="O30" s="18" t="inlineStr">
-        <is>
-          <t>P | 383呎 (2房)
-$634万
-$16,564/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="P30" s="18" t="inlineStr">
-        <is>
-          <t>Q | 443呎 (2房)
-$797万
-$18,000/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +154,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +229,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +662,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -36197,4 +36385,6732 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N4" s="19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P4" s="19" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M5" s="20" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O5" s="20" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P5" s="20" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M6" s="20" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O6" s="20" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P6" s="20" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M7" s="20" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N7" s="20" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O7" s="20" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P7" s="20" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M8" s="20" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N8" s="20" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O8" s="20" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P8" s="20" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M9" s="20" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N9" s="20" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P9" s="20" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M10" s="20" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N10" s="20" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O10" s="20" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O11" s="20" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$921万
+$24,050/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+-
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M12" s="20" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$1184万
+$26,417/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$896万
+$23,394/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$899万
+$23,462/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$618万
+$23,595/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$924万
+$23,579/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$1084万
+$28,153/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$842万
+$29,334/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M13" s="23" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+$1090万
+$27,605/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="N13" s="23" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+$1151万
+$28,561/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="O13" s="21" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P13" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$1019万
+$23,327/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+$898万
+$22,722/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$874万
+$22,825/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$877万
+$22,890/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$570万
+$21,744/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$1052万
+$27,332/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$826万
+$28,777/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M14" s="23" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+$1059万
+$26,803/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="N14" s="23" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+$1118万
+$27,730/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="O14" s="21" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P14" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$1047万
+$23,968/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+$870万
+$22,355/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+$876万
+$22,167/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$853万
+$22,266/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$808万
+$21,097/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$556万
+$21,218/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$889万
+$22,668/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$818万
+$28,505/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M15" s="21" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="N15" s="21" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O15" s="22" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+$952万
+$23,867/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="P15" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$1027万
+$23,503/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+$820万
+$21,080/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+$858万
+$21,734/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$790万
+$20,616/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$792万
+$20,681/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$545万
+$20,802/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$862万
+$22,003/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$658万
+$22,927/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K16" s="22" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+$864万
+$22,370/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L16" s="22" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+$852万
+$22,370/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M16" s="21" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="N16" s="21" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O16" s="22" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+$915万
+$22,942/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="P16" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$997万
+$22,819/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$949万
+$21,192/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+$804万
+$20,668/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+$748万
+$18,927/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$746万
+$19,480/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$792万
+$20,668/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$522万
+$19,908/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$799万
+$20,372/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$645万
+$22,488/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+$847万
+$21,933/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L17" s="22" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+$836万
+$21,932/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="M17" s="21" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="N17" s="22" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+$896万
+$22,241/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O17" s="22" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+$840万
+$21,048/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="P17" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$906万
+$20,728/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$870万
+$19,426/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+$736万
+$18,910/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+$733万
+$18,549/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$731万
+$19,094/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$719万
+$18,773/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$512万
+$19,523/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$783万
+$19,977/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$633万
+$22,059/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+$822万
+$21,288/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L18" s="22" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+$811万
+$21,289/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="M18" s="22" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+$850万
+$21,514/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="N18" s="22" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+$870万
+$21,593/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O18" s="22" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+$815万
+$20,436/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="P18" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$879万
+$20,124/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$878万
+$19,607/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+$721万
+$18,530/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+$718万
+$18,180/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$717万
+$18,713/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$705万
+$18,405/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$513万
+$19,595/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$768万
+$19,582/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$819万
+$21,275/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$611万
+$21,286/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K19" s="22" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+$761万
+$19,710/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="L19" s="22" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+$751万
+$19,711/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="M19" s="22" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+$801万
+$20,286/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="N19" s="22" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+$790万
+$19,613/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="O19" s="22" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+$792万
+$19,840/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="P19" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$854万
+$19,535/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$836万
+$18,672/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+$698万
+$17,931/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+$695万
+$17,590/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$685万
+$17,890/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$691万
+$18,044/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$500万
+$19,095/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$743万
+$18,957/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$755万
+$19,610/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$606万
+$21,105/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K20" s="22" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+$739万
+$19,137/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="L20" s="22" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+$729万
+$19,136/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="M20" s="22" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+$756万
+$19,137/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="N20" s="22" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+$775万
+$19,228/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="O20" s="22" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+$776万
+$19,449/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="P20" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$837万
+$19,153/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$832万
+$18,580/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+$684万
+$17,571/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+$683万
+$17,281/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$673万
+$17,577/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$661万
+$17,269/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$470万
+$17,958/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$730万
+$18,630/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$737万
+$19,132/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$560万
+$19,498/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K21" s="22" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+$717万
+$18,580/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="L21" s="22" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+$708万
+$18,580/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="M21" s="22" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+$734万
+$18,580/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="N21" s="22" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+$760万
+$18,851/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="O21" s="22" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+$761万
+$19,068/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="P21" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$821万
+$18,778/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$808万
+$18,038/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+$663万
+$17,049/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+$671万
+$16,980/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$662万
+$17,274/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$642万
+$16,765/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$476万
+$18,179/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$718万
+$18,309/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$718万
+$18,662/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$555万
+$19,341/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+$696万
+$18,039/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="L22" s="22" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+$687万
+$18,037/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M22" s="22" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+$712万
+$18,038/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="N22" s="22" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+$745万
+$18,481/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="O22" s="22" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+$746万
+$18,694/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="P22" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$804万
+$18,410/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$896万
+$20,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+$657万
+$16,879/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+$659万
+$16,681/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$650万
+$16,971/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$639万
+$16,681/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$454万
+$17,347/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$705万
+$17,992/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$700万
+$18,182/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$539万
+$18,777/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+$712万
+$18,451/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+$762万
+$20,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="M23" s="22" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+$729万
+$18,451/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="N23" s="22" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+$716万
+$17,772/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="O23" s="22" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+$738万
+$18,509/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="P23" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$796万
+$18,217/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$905万
+$20,201/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+$654万
+$16,820/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+$652万
+$16,501/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$674万
+$17,595/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$636万
+$16,601/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$452万
+$17,263/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$686万
+$17,513/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$693万
+$17,997/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$534万
+$18,596/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+$772万
+$20,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+$703万
+$18,451/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="M24" s="22" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+$798万
+$20,203/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N24" s="22" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+$709万
+$17,596/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="O24" s="22" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+$718万
+$18,003/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="P24" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$788万
+$18,034/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$784万
+$17,509/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+$648万
+$16,656/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+$648万
+$16,418/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$670万
+$17,507/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$656万
+$17,120/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$450万
+$17,172/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$683万
+$17,426/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$686万
+$17,816/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$528万
+$18,404/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+$772万
+$20,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L25" s="22" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+$762万
+$20,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="M25" s="22" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+$798万
+$20,203/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N25" s="22" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+$706万
+$17,506/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="O25" s="22" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+$715万
+$17,912/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="P25" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$769万
+$17,593/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$780万
+$17,420/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+$645万
+$16,571/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+$645万
+$16,337/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$667万
+$17,420/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$652万
+$17,034/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$464万
+$17,714/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$680万
+$17,339/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$682万
+$17,727/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$523万
+$18,223/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+$733万
+$19,000/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="L26" s="22" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+$686万
+$18,000/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="M26" s="21" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="N26" s="22" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+$725万
+$18,000/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="O26" s="22" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+$698万
+$17,504/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="P26" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$765万
+$17,503/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$777万
+$17,335/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+$641万
+$16,488/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+$642万
+$16,253/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$664万
+$17,334/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$636万
+$16,619/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$446万
+$17,004/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$676万
+$17,253/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$770万
+$20,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$533万
+$18,568/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+$772万
+$20,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L27" s="22" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+$724万
+$19,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="M27" s="21" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="N27" s="22" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+$725万
+$18,000/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="O27" s="22" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+$695万
+$17,416/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="P27" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$761万
+$17,416/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 447呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$675万
+$17,297/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+$674万
+$17,053/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$663万
+$17,300/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 384呎 (2房)
+$650万
+$16,917/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$438万
+$16,721/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$706万
+$18,000/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$530万
+$18,474/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="inlineStr">
+        <is>
+          <t>K | 387呎 (2房)
+$716万
+$18,501/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="L28" s="22" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+$705万
+$18,501/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="M28" s="21" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="N28" s="21" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O28" s="22" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+$738万
+$18,501/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="P28" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$757万
+$17,330/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>A | 447呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$659万
+$16,903/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+$668万
+$16,904/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$647万
+$16,903/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>E | 384呎 (2房)
+$636万
+$16,565/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$454万
+$17,321/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$706万
+$18,000/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="J29" s="22" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$543万
+$18,923/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>K | 387呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="L29" s="22" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+$770万
+$20,202/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="M29" s="21" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="N29" s="21" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O29" s="22" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+$806万
+$20,201/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="P29" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$883万
+$20,201/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N4" s="19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P4" s="19" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M5" s="20" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O5" s="20" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P5" s="20" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M6" s="20" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O6" s="20" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P6" s="20" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M7" s="20" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N7" s="20" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O7" s="20" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P7" s="20" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M8" s="20" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N8" s="20" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O8" s="20" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P8" s="20" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M9" s="20" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O9" s="21" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P9" s="20" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+$1136万
+$25,177/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$820万
+$31,290/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M10" s="20" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O10" s="21" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P10" s="20" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+$1108万
+$24,561/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$954万
+$24,903/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$800万
+$30,527/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K11" s="21" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M11" s="21" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="N11" s="22" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+$866万
+$22,608/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O11" s="22" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+$882万
+$23,037/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+$1081万
+$23,962/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$930万
+$24,295/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+$899万
+$22,931/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$927万
+$24,211/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$640万
+$24,420/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$888万
+$22,663/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M12" s="21" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="N12" s="22" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+$849万
+$22,167/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O12" s="22" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+$865万
+$22,587/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$1027万
+$26,815/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$1013万
+$26,452/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$761万
+$29,057/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M13" s="20" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N13" s="20" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O13" s="20" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P13" s="20" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+$972万
+$21,545/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$822万
+$21,449/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+$830万
+$21,186/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+$880万
+$22,220/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$826万
+$21,569/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$572万
+$21,813/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$837万
+$21,362/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$830万
+$21,564/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+$655万
+$23,145/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+$880万
+$22,384/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M14" s="21" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="N14" s="22" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+$771万
+$20,125/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="O14" s="22" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+$785万
+$20,504/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="P14" s="22" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+$962万
+$21,725/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+$948万
+$21,022/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$817万
+$21,334/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+$806万
+$20,569/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+$858万
+$21,679/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$806万
+$21,044/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$561万
+$21,420/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$817万
+$20,842/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$871万
+$22,613/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+$649万
+$22,933/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+$814万
+$20,725/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M15" s="22" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+$783万
+$19,718/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="N15" s="22" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+$707万
+$18,460/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="O15" s="22" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+$720万
+$18,809/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="P15" s="22" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+$944万
+$21,298/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+$909万
+$20,162/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$793万
+$20,713/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+$764万
+$19,485/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+$787万
+$19,864/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$806万
+$21,034/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$559万
+$21,344/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$744万
+$18,972/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$849万
+$22,062/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+$626万
+$22,134/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K16" s="22" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+$799万
+$20,321/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L16" s="22" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+$823万
+$20,125/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M16" s="22" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+$817万
+$20,574/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="N16" s="22" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+$693万
+$18,099/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="O16" s="22" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+$719万
+$18,781/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="P16" s="22" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+$874万
+$19,720/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+$904万
+$20,055/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$770万
+$20,107/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+$755万
+$19,270/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+$783万
+$19,763/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$792万
+$20,668/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$497万
+$18,958/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$731万
+$18,645/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$797万
+$20,706/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+$614万
+$21,710/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+$783万
+$19,921/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M17" s="22" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+$760万
+$19,136/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="N17" s="22" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+$688万
+$17,961/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="O17" s="22" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+$705万
+$18,410/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="P17" s="22" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+$856万
+$19,334/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+$895万
+$19,854/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$787万
+$20,538/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+$751万
+$19,153/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+$773万
+$19,525/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$699万
+$18,253/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$487万
+$18,584/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$729万
+$18,589/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$778万
+$20,197/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+$573万
+$20,233/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+$768万
+$19,532/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M18" s="22" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+$748万
+$18,854/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="N18" s="22" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+$700万
+$18,279/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="O18" s="22" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+$679万
+$17,726/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="P18" s="22" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+$840万
+$18,953/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+$892万
+$19,772/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$723万
+$18,867/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+$736万
+$18,768/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+$769万
+$19,417/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$685万
+$17,893/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$477万
+$18,214/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$714万
+$18,227/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$726万
+$18,852/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+$542万
+$19,152/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="K19" s="22" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+$752万
+$19,148/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L19" s="22" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+$821万
+$20,081/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="M19" s="22" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+$738万
+$18,577/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="N19" s="22" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+$664万
+$17,342/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="O19" s="22" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+$688万
+$17,977/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="P19" s="22" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+$779万
+$17,580/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+$927万
+$20,554/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$708万
+$18,499/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+$721万
+$18,393/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+$766万
+$19,333/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$672万
+$17,540/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$468万
+$17,859/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$700万
+$17,870/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$720万
+$18,709/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+$531万
+$18,777/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K20" s="22" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+$738万
+$18,771/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L20" s="22" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+$760万
+$18,592/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M20" s="22" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+$727万
+$18,302/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="N20" s="22" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+$654万
+$17,086/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="O20" s="22" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+$666万
+$17,376/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="P20" s="22" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+$771万
+$17,406/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+$853万
+$18,914/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$692万
+$18,063/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+$707万
+$18,028/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+$722万
+$18,242/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$659万
+$17,196/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$459万
+$17,504/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$715万
+$18,247/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$715万
+$18,564/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+$527万
+$18,629/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K21" s="22" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+$723万
+$18,405/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="L21" s="22" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+$746万
+$18,227/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M21" s="22" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+$716万
+$18,030/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="N21" s="22" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+$648万
+$16,916/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="O21" s="22" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+$659万
+$17,201/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="P21" s="24" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+$930万
+$20,982/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+$835万
+$18,508/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$668万
+$17,436/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+$692万
+$17,666/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+$701万
+$17,707/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$667万
+$17,407/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$445万
+$16,989/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$673万
+$17,173/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$710万
+$18,444/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+$524万
+$18,523/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+$709万
+$18,043/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M22" s="22" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+$705万
+$17,763/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="N22" s="22" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+$641万
+$16,747/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="O22" s="22" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+$652万
+$17,031/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="P22" s="22" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+$741万
+$16,722/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+$802万
+$17,776/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$664万
+$17,350/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+$656万
+$16,724/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+$693万
+$17,497/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$636万
+$16,608/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$443万
+$16,905/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$670万
+$17,089/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$807万
+$20,958/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+$486万
+$17,166/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>K | 393呎 (2房)
+$688万
+$17,517/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+$710万
+$17,350/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="M23" s="22" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+$685万
+$17,247/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="N23" s="22" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+$635万
+$16,582/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="O23" s="22" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+$643万
+$16,789/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="P23" s="22" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+$734万
+$16,558/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+$784万
+$17,379/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$685万
+$17,896/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+$665万
+$16,969/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+$673万
+$17,005/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$633万
+$16,527/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$441万
+$16,821/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$667万
+$17,005/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$639万
+$16,608/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+$472万
+$16,664/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>K | 394呎 (2房)
+$687万
+$17,429/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M24" s="22" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+$683万
+$17,194/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="N24" s="22" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+$648万
+$16,906/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="O24" s="22" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+$646万
+$16,864/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="P24" s="22" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+$732万
+$16,533/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+$761万
+$16,882/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$669万
+$17,473/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+$649万
+$16,559/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+$657万
+$16,598/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$630万
+$16,444/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$441万
+$16,844/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$650万
+$16,594/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$636万
+$16,527/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+$469万
+$16,580/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>K | 394呎 (2房)
+$683万
+$17,343/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="L25" s="21" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M25" s="21" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="N25" s="22" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+$654万
+$17,089/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="O25" s="22" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+$631万
+$16,486/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="P25" s="22" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+$730万
+$16,483/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+$754万
+$16,712/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$666万
+$17,384/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+$646万
+$16,474/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+$654万
+$16,513/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$627万
+$16,360/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$436万
+$16,656/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$647万
+$16,508/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$633万
+$16,444/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+$467万
+$16,498/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>K | 394呎 (2房)
+$680万
+$17,256/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M26" s="22" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+$715万
+$18,000/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="N26" s="22" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+$640万
+$16,700/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="O26" s="22" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+$629万
+$16,433/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="P26" s="22" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+$728万
+$16,436/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+$747万
+$16,554/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$662万
+$17,298/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+$829万
+$21,148/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+$651万
+$16,429/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$811万
+$21,164/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$434万
+$16,573/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$644万
+$16,426/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$656万
+$17,039/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+$484万
+$17,120/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>K | 394呎 (2房)
+$677万
+$17,173/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="L27" s="21" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M27" s="21" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="N27" s="22" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+$638万
+$16,650/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="O27" s="22" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+$615万
+$16,050/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="P27" s="22" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+$726万
+$16,386/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 450呎 (2房)
+$744万
+$16,538/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$648万
+$16,924/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+$639万
+$16,309/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+$649万
+$16,394/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$622万
+$16,245/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$425万
+$16,210/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$642万
+$16,390/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$640万
+$16,618/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+$482万
+$17,032/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="inlineStr">
+        <is>
+          <t>K | 394呎 (2房)
+$709万
+$18,000/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="L28" s="21" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M28" s="21" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="N28" s="22" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+$636万
+$16,601/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="O28" s="22" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+$636万
+$16,601/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="P28" s="22" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+$724万
+$16,336/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 450呎 (2房)
+$741万
+$16,467/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 383呎 (2房)
+$627万
+$16,371/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 392呎 (2房)
+$634万
+$16,176/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 396呎 (2房)
+$661万
+$16,702/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$624万
+$16,303/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$424万
+$16,202/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$642万
+$16,375/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$712万
+$18,501/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J29" s="22" t="inlineStr">
+        <is>
+          <t>J | 283呎 (1房)
+$478万
+$16,898/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>K | 394呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
+        <is>
+          <t>L | 409呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="M29" s="21" t="inlineStr">
+        <is>
+          <t>M | 397呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="N29" s="22" t="inlineStr">
+        <is>
+          <t>N | 383呎 (2房)
+$634万
+$16,564/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="O29" s="22" t="inlineStr">
+        <is>
+          <t>P | 383呎 (2房)
+$634万
+$16,564/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="P29" s="22" t="inlineStr">
+        <is>
+          <t>Q | 443呎 (2房)
+$797万
+$18,000/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -662,7 +662,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -8464,19 +8464,19 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
-        <v>8181000</v>
+        <v>6708000</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>28505</v>
+        <v>23373</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
@@ -36461,7 +36461,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -36471,7 +36471,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>212</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -37907,12 +37907,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J15" s="21" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>J | 287呎 (1房)
-$818万
-$28,505/呎
-(在售)</t>
+$671万
+$23,373/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">

--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -31146,14 +31146,14 @@
       </c>
       <c r="J462" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K462" s="5" t="n">
-        <v>6722360</v>
+        <v>7132260</v>
       </c>
       <c r="L462" s="5" t="n">
-        <v>25658</v>
+        <v>27222</v>
       </c>
       <c r="M462" s="3" t="inlineStr">
         <is>
@@ -32164,14 +32164,14 @@
       </c>
       <c r="J477" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K477" s="5" t="n">
-        <v>6558360</v>
+        <v>6958260</v>
       </c>
       <c r="L477" s="5" t="n">
-        <v>25032</v>
+        <v>26558</v>
       </c>
       <c r="M477" s="3" t="inlineStr">
         <is>
@@ -34176,14 +34176,14 @@
       </c>
       <c r="J507" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K507" s="5" t="n">
-        <v>6242660</v>
+        <v>6623310</v>
       </c>
       <c r="L507" s="5" t="n">
-        <v>23827</v>
+        <v>25280</v>
       </c>
       <c r="M507" s="3" t="inlineStr">
         <is>
@@ -34238,14 +34238,14 @@
       </c>
       <c r="J508" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="K508" s="5" t="n">
-        <v>8307420</v>
+        <v>9523140</v>
       </c>
       <c r="L508" s="5" t="n">
-        <v>21690</v>
+        <v>24865</v>
       </c>
       <c r="M508" s="3" t="inlineStr">
         <is>
@@ -34440,14 +34440,14 @@
       </c>
       <c r="J511" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="K511" s="5" t="n">
-        <v>8421400</v>
+        <v>9653800</v>
       </c>
       <c r="L511" s="5" t="n">
-        <v>21988</v>
+        <v>25206</v>
       </c>
       <c r="M511" s="3" t="inlineStr">
         <is>
@@ -41133,7 +41133,7 @@
       </c>
       <c r="M618" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>150天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N618" s="3" t="inlineStr">
@@ -43424,18 +43424,18 @@
       </c>
       <c r="J655" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="K655" s="5" t="n">
-        <v>6616580</v>
+        <v>7584860</v>
       </c>
       <c r="L655" s="5" t="n">
-        <v>17186</v>
+        <v>19701</v>
       </c>
       <c r="M655" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>150天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N655" s="3" t="inlineStr">

--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -8888,38 +8888,30 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I119" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>9184000</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>23979</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K119" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L119" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K119" s="5" t="n">
+        <v>9184000</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>23979</v>
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
@@ -8928,7 +8920,7 @@
       </c>
       <c r="N119" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -11121,7 +11113,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -11657,7 +11649,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -31130,34 +31122,34 @@
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
-        <v>8198000</v>
+        <v>6722000</v>
       </c>
       <c r="I462" s="5" t="n">
-        <v>31290</v>
+        <v>25656</v>
       </c>
       <c r="J462" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K462" s="5" t="n">
-        <v>7132260</v>
+        <v>6722000</v>
       </c>
       <c r="L462" s="5" t="n">
-        <v>27222</v>
+        <v>25656</v>
       </c>
       <c r="M462" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N462" s="3" t="inlineStr">
@@ -32148,34 +32140,34 @@
       </c>
       <c r="F477" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H477" s="5" t="n">
-        <v>7998000</v>
+        <v>6558000</v>
       </c>
       <c r="I477" s="5" t="n">
-        <v>30527</v>
+        <v>25031</v>
       </c>
       <c r="J477" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K477" s="5" t="n">
-        <v>6958260</v>
+        <v>6558000</v>
       </c>
       <c r="L477" s="5" t="n">
-        <v>26558</v>
+        <v>25031</v>
       </c>
       <c r="M477" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N477" s="3" t="inlineStr">
@@ -34561,7 +34553,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H513" s="5" t="n">
@@ -34949,7 +34941,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H519" s="5" t="n">
@@ -35949,7 +35941,7 @@
       </c>
       <c r="G535" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H535" s="5" t="n">
@@ -49629,7 +49621,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -49639,7 +49631,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>215</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -50654,12 +50646,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 383呎 (2房)
-招标单位
--
-(在售)</t>
+$918万
+$23,979/呎
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -51064,7 +51056,7 @@
           <t>G | 392呎 (2房)
 $889万
 $22,668/呎
-(26年-06月-26日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -51128,7 +51120,7 @@
           <t>Q | 437呎 (2房)
 $1027万
 $23,503/呎
-(26年-06月-14日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -52993,7 +52985,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -53003,7 +52995,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>236</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -53780,12 +53772,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
-$820万
-$31,290/呎
-(在售)</t>
+$672万
+$25,656/呎
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -53907,12 +53899,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
-$800万
-$30,527/呎
-(在售)</t>
+$656万
+$25,031/呎
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -54317,7 +54309,7 @@
           <t>J | 283呎 (1房)
 $655万
 $23,145/呎
-(26年-06月-22日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -54365,7 +54357,7 @@
           <t>Q | 443呎 (2房)
 $962万
 $21,725/呎
-(26年-06月-19日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -54436,7 +54428,7 @@
           <t>H | 385呎 (2房)
 $871万
 $22,613/呎
-(26年-06月-10日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
